--- a/tracking/compare/tracking-list.xlsx
+++ b/tracking/compare/tracking-list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA00B5D-5C55-49D7-941A-AE7BA8E7252E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07E0F82-2E99-4007-BD1A-DCE8F22DEFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D2D124BC-3906-40C8-BA6E-71B75F658845}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D2D124BC-3906-40C8-BA6E-71B75F658845}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="264">
   <si>
     <t>ID</t>
   </si>
@@ -781,6 +781,42 @@
   </si>
   <si>
     <t>무지개마을대림</t>
+  </si>
+  <si>
+    <t>철산역 롯데캐슬&amp;SK VIEW 클래스티지</t>
+  </si>
+  <si>
+    <t>광명푸르지오포레나</t>
+  </si>
+  <si>
+    <t>롯데캐슬골드파크1차</t>
+  </si>
+  <si>
+    <t>철산래미안자이</t>
+  </si>
+  <si>
+    <t>신촌휴먼시아1단지</t>
+  </si>
+  <si>
+    <t>광명역센트럴자이(주상복합)</t>
+  </si>
+  <si>
+    <t>가산두산위브</t>
+  </si>
+  <si>
+    <t>주공1단지</t>
+  </si>
+  <si>
+    <t>주공8단지</t>
+  </si>
+  <si>
+    <t>남서울힐스테이트</t>
+  </si>
+  <si>
+    <t>광명역세권휴멍시아4단지</t>
+  </si>
+  <si>
+    <t>관악벽산타운5단지</t>
   </si>
 </sst>
 </file>
@@ -1260,7 +1296,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A24302-B46C-46ED-B213-366C3ADB75BA}">
-  <dimension ref="A1:C252"/>
+  <dimension ref="A1:C264"/>
   <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="39.69921875" customWidth="1"/>
@@ -4038,6 +4074,138 @@
         <v>84</v>
       </c>
     </row>
+    <row r="253" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A253" s="8">
+        <v>127424</v>
+      </c>
+      <c r="B253" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="C253" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A254" s="7">
+        <v>133083</v>
+      </c>
+      <c r="B254" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C254" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A255" s="8">
+        <v>107929</v>
+      </c>
+      <c r="B255" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C255" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A256" s="8">
+        <v>25902</v>
+      </c>
+      <c r="B256" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C256" s="11">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A257" s="8">
+        <v>27821</v>
+      </c>
+      <c r="B257" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C257" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A258" s="8">
+        <v>111972</v>
+      </c>
+      <c r="B258" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C258" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A259" s="8">
+        <v>159</v>
+      </c>
+      <c r="B259" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C259" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A260" s="8">
+        <v>1627</v>
+      </c>
+      <c r="B260" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C260" s="11">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A261" s="7">
+        <v>1635</v>
+      </c>
+      <c r="B261" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C261" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A262" s="8">
+        <v>104347</v>
+      </c>
+      <c r="B262" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C262" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A263" s="7">
+        <v>100253</v>
+      </c>
+      <c r="B263" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C263" s="11">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A264" s="8">
+        <v>3359</v>
+      </c>
+      <c r="B264" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C264" s="11">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tracking/compare/tracking-list.xlsx
+++ b/tracking/compare/tracking-list.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\markc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\roy\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E07E0F82-2E99-4007-BD1A-DCE8F22DEFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDCFE36B-87DB-4271-871B-C073992232F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{D2D124BC-3906-40C8-BA6E-71B75F658845}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D2D124BC-3906-40C8-BA6E-71B75F658845}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="276">
   <si>
     <t>ID</t>
   </si>
@@ -817,13 +828,49 @@
   </si>
   <si>
     <t>관악벽산타운5단지</t>
+  </si>
+  <si>
+    <t>안양역푸르지오더샵</t>
+  </si>
+  <si>
+    <t>래미안안양메가트리아</t>
+  </si>
+  <si>
+    <t>석수두산위브</t>
+  </si>
+  <si>
+    <t>석수역푸르지오</t>
+  </si>
+  <si>
+    <t>석수2차e-편한세상</t>
+  </si>
+  <si>
+    <t>힐스테이트석수</t>
+  </si>
+  <si>
+    <t>석수e-편한세상</t>
+  </si>
+  <si>
+    <t>안양어반포레자연앤e편한세상</t>
+  </si>
+  <si>
+    <t>안양씨엘포레자이</t>
+  </si>
+  <si>
+    <t>안양자이더포레스트</t>
+  </si>
+  <si>
+    <t>석수아이파크</t>
+  </si>
+  <si>
+    <t>한신휴플러스타운3차</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="9"/>
       <color theme="1"/>
@@ -1000,9 +1047,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1040,7 +1087,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1146,7 +1193,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1288,7 +1335,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1296,13 +1343,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A24302-B46C-46ED-B213-366C3ADB75BA}">
-  <dimension ref="A1:C264"/>
-  <sheetFormatPr defaultRowHeight="12.6" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C276"/>
+  <sheetFormatPr defaultRowHeight="10.8"/>
   <cols>
-    <col min="2" max="2" width="39.69921875" customWidth="1"/>
+    <col min="2" max="2" width="39.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="13.8" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1313,7 +1360,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="13.8" thickBot="1">
       <c r="A2" s="3">
         <v>113292</v>
       </c>
@@ -1324,7 +1371,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="13.8" thickBot="1">
       <c r="A3" s="4">
         <v>131685</v>
       </c>
@@ -1335,7 +1382,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="13.8" thickBot="1">
       <c r="A4" s="3">
         <v>100304</v>
       </c>
@@ -1346,7 +1393,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="13.8" thickBot="1">
       <c r="A5" s="4">
         <v>109124</v>
       </c>
@@ -1357,7 +1404,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="13.8" thickBot="1">
       <c r="A6" s="3">
         <v>113097</v>
       </c>
@@ -1368,7 +1415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="13.8" thickBot="1">
       <c r="A7" s="4">
         <v>22491</v>
       </c>
@@ -1379,7 +1426,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="13.8" thickBot="1">
       <c r="A8" s="3">
         <v>3381</v>
       </c>
@@ -1390,7 +1437,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="13.8" thickBot="1">
       <c r="A9" s="4">
         <v>364</v>
       </c>
@@ -1401,7 +1448,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="13.8" thickBot="1">
       <c r="A10" s="3">
         <v>3280</v>
       </c>
@@ -1412,7 +1459,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="13.8" thickBot="1">
       <c r="A11" s="4">
         <v>102142</v>
       </c>
@@ -1423,7 +1470,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="13.8" thickBot="1">
       <c r="A12" s="3">
         <v>111467</v>
       </c>
@@ -1434,7 +1481,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="13.8" thickBot="1">
       <c r="A13" s="4">
         <v>115936</v>
       </c>
@@ -1445,7 +1492,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="13.8" thickBot="1">
       <c r="A14" s="3">
         <v>391</v>
       </c>
@@ -1456,7 +1503,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="13.8" thickBot="1">
       <c r="A15" s="4">
         <v>123898</v>
       </c>
@@ -1467,7 +1514,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" ht="13.8" thickBot="1">
       <c r="A16" s="3">
         <v>27508</v>
       </c>
@@ -1478,7 +1525,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="13.8" thickBot="1">
       <c r="A17" s="4">
         <v>27570</v>
       </c>
@@ -1489,7 +1536,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="13.8" thickBot="1">
       <c r="A18" s="3">
         <v>27371</v>
       </c>
@@ -1500,7 +1547,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="13.8" thickBot="1">
       <c r="A19" s="4">
         <v>3621</v>
       </c>
@@ -1511,7 +1558,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="13.8" thickBot="1">
       <c r="A20" s="3">
         <v>2623</v>
       </c>
@@ -1522,7 +1569,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="13.8" thickBot="1">
       <c r="A21" s="4">
         <v>2797</v>
       </c>
@@ -1533,7 +1580,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="13.8" thickBot="1">
       <c r="A22" s="3">
         <v>1980</v>
       </c>
@@ -1544,7 +1591,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="13.8" thickBot="1">
       <c r="A23" s="4">
         <v>1923</v>
       </c>
@@ -1555,7 +1602,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="13.8" thickBot="1">
       <c r="A24" s="3">
         <v>1687</v>
       </c>
@@ -1566,7 +1613,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="13.8" thickBot="1">
       <c r="A25" s="4">
         <v>8297</v>
       </c>
@@ -1577,7 +1624,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="13.8" thickBot="1">
       <c r="A26" s="3">
         <v>2591</v>
       </c>
@@ -1588,7 +1635,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="13.8" thickBot="1">
       <c r="A27" s="4">
         <v>2789</v>
       </c>
@@ -1599,7 +1646,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="13.8" thickBot="1">
       <c r="A28" s="3">
         <v>1525</v>
       </c>
@@ -1610,7 +1657,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="13.8" thickBot="1">
       <c r="A29" s="4">
         <v>2537</v>
       </c>
@@ -1621,7 +1668,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" ht="13.8" thickBot="1">
       <c r="A30" s="3">
         <v>2198</v>
       </c>
@@ -1632,7 +1679,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="13.8" thickBot="1">
       <c r="A31" s="4">
         <v>3457</v>
       </c>
@@ -1643,7 +1690,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" ht="13.8" thickBot="1">
       <c r="A32" s="3">
         <v>2981</v>
       </c>
@@ -1654,7 +1701,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="13.8" thickBot="1">
       <c r="A33" s="4">
         <v>121987</v>
       </c>
@@ -1665,7 +1712,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="13.8" thickBot="1">
       <c r="A34" s="3">
         <v>3452</v>
       </c>
@@ -1676,7 +1723,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="13.8" thickBot="1">
       <c r="A35" s="4">
         <v>3450</v>
       </c>
@@ -1687,7 +1734,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="13.8" thickBot="1">
       <c r="A36" s="3">
         <v>1216</v>
       </c>
@@ -1698,7 +1745,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="13.8" thickBot="1">
       <c r="A37" s="4">
         <v>120522</v>
       </c>
@@ -1709,7 +1756,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" ht="13.8" thickBot="1">
       <c r="A38" s="3">
         <v>117254</v>
       </c>
@@ -1720,7 +1767,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="13.8" thickBot="1">
       <c r="A39" s="4">
         <v>128302</v>
       </c>
@@ -1731,7 +1778,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="13.8" thickBot="1">
       <c r="A40" s="5">
         <v>111396</v>
       </c>
@@ -1742,7 +1789,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="13.8" thickBot="1">
       <c r="A41" s="5">
         <v>103797</v>
       </c>
@@ -1753,7 +1800,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="13.8" thickBot="1">
       <c r="A42" s="5">
         <v>113059</v>
       </c>
@@ -1764,7 +1811,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="13.8" thickBot="1">
       <c r="A43" s="5">
         <v>125111</v>
       </c>
@@ -1775,7 +1822,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="13.8" thickBot="1">
       <c r="A44" s="5">
         <v>133184</v>
       </c>
@@ -1786,7 +1833,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="13.8" thickBot="1">
       <c r="A45" s="5">
         <v>26192</v>
       </c>
@@ -1797,7 +1844,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="13.8" thickBot="1">
       <c r="A46" s="5">
         <v>3376</v>
       </c>
@@ -1808,7 +1855,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" ht="13.8" thickBot="1">
       <c r="A47" s="5">
         <v>22636</v>
       </c>
@@ -1819,7 +1866,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" ht="13.8" thickBot="1">
       <c r="A48" s="5">
         <v>119787</v>
       </c>
@@ -1830,7 +1877,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="13.8" thickBot="1">
       <c r="A49" s="5">
         <v>112482</v>
       </c>
@@ -1841,7 +1888,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="13.8" thickBot="1">
       <c r="A50" s="5">
         <v>8199</v>
       </c>
@@ -1852,7 +1899,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="13.8" thickBot="1">
       <c r="A51" s="5">
         <v>8791</v>
       </c>
@@ -1863,7 +1910,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="13.8" thickBot="1">
       <c r="A52" s="4">
         <v>111555</v>
       </c>
@@ -1874,7 +1921,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" ht="13.8" thickBot="1">
       <c r="A53" s="3">
         <v>120540</v>
       </c>
@@ -1885,7 +1932,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="13.8" thickBot="1">
       <c r="A54" s="4">
         <v>3093</v>
       </c>
@@ -1896,7 +1943,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="13.8" thickBot="1">
       <c r="A55" s="3">
         <v>102536</v>
       </c>
@@ -1907,7 +1954,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="13.8" thickBot="1">
       <c r="A56" s="4">
         <v>8484</v>
       </c>
@@ -1918,7 +1965,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="13.8" thickBot="1">
       <c r="A57" s="3">
         <v>109948</v>
       </c>
@@ -1929,7 +1976,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="13.8" thickBot="1">
       <c r="A58" s="4">
         <v>115593</v>
       </c>
@@ -1940,7 +1987,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="13.8" thickBot="1">
       <c r="A59" s="3">
         <v>9390</v>
       </c>
@@ -1951,7 +1998,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="13.8" thickBot="1">
       <c r="A60" s="4">
         <v>126607</v>
       </c>
@@ -1962,7 +2009,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="13.8" thickBot="1">
       <c r="A61" s="3">
         <v>8292</v>
       </c>
@@ -1973,7 +2020,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" ht="13.8" thickBot="1">
       <c r="A62" s="4">
         <v>2535</v>
       </c>
@@ -1984,7 +2031,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="13.8" thickBot="1">
       <c r="A63" s="3">
         <v>24301</v>
       </c>
@@ -1995,7 +2042,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="13.8" thickBot="1">
       <c r="A64" s="4">
         <v>119652</v>
       </c>
@@ -2006,7 +2053,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" ht="13.8" thickBot="1">
       <c r="A65" s="3">
         <v>105414</v>
       </c>
@@ -2017,7 +2064,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="13.8" thickBot="1">
       <c r="A66" s="4">
         <v>107542</v>
       </c>
@@ -2028,7 +2075,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="13.8" thickBot="1">
       <c r="A67" s="3">
         <v>19204</v>
       </c>
@@ -2039,7 +2086,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="13.8" thickBot="1">
       <c r="A68" s="4">
         <v>19672</v>
       </c>
@@ -2050,7 +2097,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="13.8" thickBot="1">
       <c r="A69" s="3">
         <v>26216</v>
       </c>
@@ -2061,7 +2108,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="13.8" thickBot="1">
       <c r="A70" s="4">
         <v>113538</v>
       </c>
@@ -2072,7 +2119,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" ht="13.8" thickBot="1">
       <c r="A71" s="3">
         <v>114379</v>
       </c>
@@ -2083,7 +2130,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="13.8" thickBot="1">
       <c r="A72" s="4">
         <v>114415</v>
       </c>
@@ -2094,7 +2141,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="13.8" thickBot="1">
       <c r="A73" s="3">
         <v>115473</v>
       </c>
@@ -2105,7 +2152,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="13.8" thickBot="1">
       <c r="A74" s="4">
         <v>119469</v>
       </c>
@@ -2116,7 +2163,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="13.8" thickBot="1">
       <c r="A75" s="3">
         <v>111626</v>
       </c>
@@ -2127,7 +2174,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" ht="13.8" thickBot="1">
       <c r="A76" s="4">
         <v>22746</v>
       </c>
@@ -2138,7 +2185,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="13.8" thickBot="1">
       <c r="A77" s="3">
         <v>22675</v>
       </c>
@@ -2149,7 +2196,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="13.8" thickBot="1">
       <c r="A78" s="4">
         <v>15011</v>
       </c>
@@ -2160,7 +2207,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="13.8" thickBot="1">
       <c r="A79" s="3">
         <v>111515</v>
       </c>
@@ -2171,7 +2218,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" ht="13.8" thickBot="1">
       <c r="A80" s="4">
         <v>103139</v>
       </c>
@@ -2182,7 +2229,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" ht="13.8" thickBot="1">
       <c r="A81" s="3">
         <v>610</v>
       </c>
@@ -2193,7 +2240,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" ht="13.8" thickBot="1">
       <c r="A82" s="4">
         <v>107544</v>
       </c>
@@ -2204,7 +2251,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="13.8" thickBot="1">
       <c r="A83" s="3">
         <v>104126</v>
       </c>
@@ -2215,7 +2262,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" ht="13.8" thickBot="1">
       <c r="A84" s="4">
         <v>26107</v>
       </c>
@@ -2226,7 +2273,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="13.8" thickBot="1">
       <c r="A85" s="3">
         <v>115046</v>
       </c>
@@ -2237,7 +2284,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" ht="13.8" thickBot="1">
       <c r="A86" s="4">
         <v>127132</v>
       </c>
@@ -2248,7 +2295,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" ht="13.8" thickBot="1">
       <c r="A87" s="3">
         <v>102313</v>
       </c>
@@ -2259,7 +2306,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" ht="13.8" thickBot="1">
       <c r="A88" s="4">
         <v>114809</v>
       </c>
@@ -2270,7 +2317,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" ht="13.8" thickBot="1">
       <c r="A89" s="3">
         <v>2988</v>
       </c>
@@ -2281,7 +2328,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="13.8" thickBot="1">
       <c r="A90" s="4">
         <v>3034</v>
       </c>
@@ -2292,7 +2339,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" ht="13.8" thickBot="1">
       <c r="A91" s="3">
         <v>148337</v>
       </c>
@@ -2303,7 +2350,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="13.8" thickBot="1">
       <c r="A92" s="4">
         <v>8877</v>
       </c>
@@ -2314,7 +2361,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="13.8" thickBot="1">
       <c r="A93" s="3">
         <v>3333</v>
       </c>
@@ -2325,7 +2372,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" ht="13.8" thickBot="1">
       <c r="A94" s="4">
         <v>19220</v>
       </c>
@@ -2336,7 +2383,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" ht="13.8" thickBot="1">
       <c r="A95" s="3">
         <v>8895</v>
       </c>
@@ -2347,7 +2394,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="13.8" thickBot="1">
       <c r="A96" s="4">
         <v>18210</v>
       </c>
@@ -2358,7 +2405,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" ht="13.8" thickBot="1">
       <c r="A97" s="3">
         <v>109379</v>
       </c>
@@ -2369,7 +2416,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" ht="13.8" thickBot="1">
       <c r="A98" s="4">
         <v>22124</v>
       </c>
@@ -2380,7 +2427,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" ht="13.8" thickBot="1">
       <c r="A99" s="3">
         <v>22788</v>
       </c>
@@ -2391,7 +2438,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" ht="13.8" thickBot="1">
       <c r="A100" s="4">
         <v>109250</v>
       </c>
@@ -2402,7 +2449,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" ht="13.8" thickBot="1">
       <c r="A101" s="3">
         <v>3832</v>
       </c>
@@ -2413,7 +2460,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" ht="13.8" thickBot="1">
       <c r="A102" s="4">
         <v>107404</v>
       </c>
@@ -2424,7 +2471,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" ht="13.8" thickBot="1">
       <c r="A103" s="3">
         <v>100310</v>
       </c>
@@ -2435,7 +2482,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" ht="13.8" thickBot="1">
       <c r="A104" s="4">
         <v>27820</v>
       </c>
@@ -2446,7 +2493,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" ht="13.8" thickBot="1">
       <c r="A105" s="3">
         <v>24845</v>
       </c>
@@ -2457,7 +2504,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" ht="13.8" thickBot="1">
       <c r="A106" s="4">
         <v>24911</v>
       </c>
@@ -2468,7 +2515,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" ht="13.8" thickBot="1">
       <c r="A107" s="3">
         <v>3833</v>
       </c>
@@ -2479,7 +2526,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" ht="13.8" thickBot="1">
       <c r="A108" s="4">
         <v>1238</v>
       </c>
@@ -2490,7 +2537,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" ht="13.8" thickBot="1">
       <c r="A109" s="3">
         <v>111330</v>
       </c>
@@ -2501,7 +2548,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" ht="13.8" thickBot="1">
       <c r="A110" s="4">
         <v>126062</v>
       </c>
@@ -2512,7 +2559,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" ht="13.8" thickBot="1">
       <c r="A111" s="3">
         <v>26160</v>
       </c>
@@ -2523,7 +2570,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" ht="13.8" thickBot="1">
       <c r="A112" s="4">
         <v>26834</v>
       </c>
@@ -2534,7 +2581,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" ht="13.8" thickBot="1">
       <c r="A113" s="3">
         <v>25827</v>
       </c>
@@ -2545,7 +2592,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" ht="13.8" thickBot="1">
       <c r="A114" s="4">
         <v>1191</v>
       </c>
@@ -2556,7 +2603,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" ht="13.8" thickBot="1">
       <c r="A115" s="3">
         <v>9348</v>
       </c>
@@ -2567,7 +2614,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" ht="13.8" thickBot="1">
       <c r="A116" s="4">
         <v>109051</v>
       </c>
@@ -2578,7 +2625,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" ht="13.8" thickBot="1">
       <c r="A117" s="3">
         <v>127574</v>
       </c>
@@ -2589,7 +2636,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" ht="13.8" thickBot="1">
       <c r="A118" s="4">
         <v>122863</v>
       </c>
@@ -2600,7 +2647,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" ht="13.8" thickBot="1">
       <c r="A119" s="3">
         <v>2990</v>
       </c>
@@ -2611,7 +2658,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" ht="13.8" thickBot="1">
       <c r="A120" s="4">
         <v>114972</v>
       </c>
@@ -2622,7 +2669,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" ht="13.8" thickBot="1">
       <c r="A121" s="3">
         <v>659</v>
       </c>
@@ -2633,7 +2680,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" ht="13.8" thickBot="1">
       <c r="A122" s="4">
         <v>1204</v>
       </c>
@@ -2644,7 +2691,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" ht="13.8" thickBot="1">
       <c r="A123" s="3">
         <v>3774</v>
       </c>
@@ -2655,7 +2702,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" ht="13.8" thickBot="1">
       <c r="A124" s="4">
         <v>121979</v>
       </c>
@@ -2666,7 +2713,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" ht="13.8" thickBot="1">
       <c r="A125" s="3">
         <v>130826</v>
       </c>
@@ -2677,7 +2724,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" ht="13.8" thickBot="1">
       <c r="A126" s="4">
         <v>17469</v>
       </c>
@@ -2688,7 +2735,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" ht="13.8" thickBot="1">
       <c r="A127" s="3">
         <v>113008</v>
       </c>
@@ -2699,7 +2746,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" ht="13.8" thickBot="1">
       <c r="A128" s="4">
         <v>10307</v>
       </c>
@@ -2710,7 +2757,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" ht="13.8" thickBot="1">
       <c r="A129" s="3">
         <v>24406</v>
       </c>
@@ -2721,7 +2768,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" ht="13.8" thickBot="1">
       <c r="A130" s="4">
         <v>117329</v>
       </c>
@@ -2732,7 +2779,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" ht="13.8" thickBot="1">
       <c r="A131" s="3">
         <v>107728</v>
       </c>
@@ -2743,7 +2790,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" ht="13.8" thickBot="1">
       <c r="A132" s="4">
         <v>135411</v>
       </c>
@@ -2754,7 +2801,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" ht="13.8" thickBot="1">
       <c r="A133" s="3">
         <v>109266</v>
       </c>
@@ -2765,7 +2812,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" ht="13.8" thickBot="1">
       <c r="A134" s="4">
         <v>110632</v>
       </c>
@@ -2776,7 +2823,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" ht="13.8" thickBot="1">
       <c r="A135" s="3">
         <v>107715</v>
       </c>
@@ -2787,7 +2834,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" ht="13.8" thickBot="1">
       <c r="A136" s="4">
         <v>118771</v>
       </c>
@@ -2798,7 +2845,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" ht="13.8" thickBot="1">
       <c r="A137" s="3">
         <v>102283</v>
       </c>
@@ -2809,7 +2856,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" ht="13.8" thickBot="1">
       <c r="A138" s="4">
         <v>1736</v>
       </c>
@@ -2820,7 +2867,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" ht="13.8" thickBot="1">
       <c r="A139" s="3">
         <v>126153</v>
       </c>
@@ -2831,7 +2878,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" ht="13.8" thickBot="1">
       <c r="A140" s="4">
         <v>118718</v>
       </c>
@@ -2842,7 +2889,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" ht="13.8" thickBot="1">
       <c r="A141" s="3">
         <v>18542</v>
       </c>
@@ -2853,7 +2900,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" ht="13.8" thickBot="1">
       <c r="A142" s="4">
         <v>27291</v>
       </c>
@@ -2864,7 +2911,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" ht="13.8" thickBot="1">
       <c r="A143" s="3">
         <v>1735</v>
       </c>
@@ -2875,7 +2922,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" ht="13.8" thickBot="1">
       <c r="A144" s="4">
         <v>26187</v>
       </c>
@@ -2886,7 +2933,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" ht="13.8" thickBot="1">
       <c r="A145" s="5">
         <v>110209</v>
       </c>
@@ -2897,7 +2944,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" ht="13.8" thickBot="1">
       <c r="A146" s="5">
         <v>110092</v>
       </c>
@@ -2908,7 +2955,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" ht="13.8" thickBot="1">
       <c r="A147" s="5">
         <v>849</v>
       </c>
@@ -2919,7 +2966,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" ht="13.8" thickBot="1">
       <c r="A148" s="5">
         <v>26046</v>
       </c>
@@ -2930,7 +2977,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" ht="13.8" thickBot="1">
       <c r="A149" s="5">
         <v>11567</v>
       </c>
@@ -2941,7 +2988,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" ht="13.8" thickBot="1">
       <c r="A150" s="5">
         <v>941</v>
       </c>
@@ -2952,7 +2999,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" ht="13.8" thickBot="1">
       <c r="A151" s="5">
         <v>108064</v>
       </c>
@@ -2963,7 +3010,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" ht="13.8" thickBot="1">
       <c r="A152" s="5">
         <v>124802</v>
       </c>
@@ -2974,7 +3021,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" ht="13.8" thickBot="1">
       <c r="A153" s="5">
         <v>945</v>
       </c>
@@ -2985,7 +3032,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" ht="13.8" thickBot="1">
       <c r="A154" s="5">
         <v>128515</v>
       </c>
@@ -2996,7 +3043,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" ht="13.8" thickBot="1">
       <c r="A155" s="5">
         <v>114768</v>
       </c>
@@ -3007,7 +3054,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" ht="13.8" thickBot="1">
       <c r="A156" s="5">
         <v>128027</v>
       </c>
@@ -3018,7 +3065,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" ht="13.8" thickBot="1">
       <c r="A157" s="5">
         <v>27424</v>
       </c>
@@ -3029,7 +3076,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" ht="13.8" thickBot="1">
       <c r="A158" s="5">
         <v>8104</v>
       </c>
@@ -3040,7 +3087,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" ht="13.8" thickBot="1">
       <c r="A159" s="5">
         <v>556</v>
       </c>
@@ -3051,7 +3098,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" ht="13.8" thickBot="1">
       <c r="A160" s="5">
         <v>110938</v>
       </c>
@@ -3062,7 +3109,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" ht="13.8" thickBot="1">
       <c r="A161" s="5">
         <v>103136</v>
       </c>
@@ -3073,7 +3120,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" ht="13.8" thickBot="1">
       <c r="A162" s="5">
         <v>1179</v>
       </c>
@@ -3084,7 +3131,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" ht="13.8" thickBot="1">
       <c r="A163" s="5">
         <v>110936</v>
       </c>
@@ -3095,7 +3142,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" ht="13.8" thickBot="1">
       <c r="A164" s="5">
         <v>109910</v>
       </c>
@@ -3106,7 +3153,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" ht="13.8" thickBot="1">
       <c r="A165" s="5">
         <v>2976</v>
       </c>
@@ -3117,7 +3164,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" ht="13.8" thickBot="1">
       <c r="A166" s="5">
         <v>10316</v>
       </c>
@@ -3128,7 +3175,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" ht="13.8" thickBot="1">
       <c r="A167" s="5">
         <v>111002</v>
       </c>
@@ -3139,7 +3186,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" ht="13.8" thickBot="1">
       <c r="A168" s="5">
         <v>9124</v>
       </c>
@@ -3150,7 +3197,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" ht="13.8" thickBot="1">
       <c r="A169" s="5">
         <v>119275</v>
       </c>
@@ -3161,7 +3208,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" ht="13.8" thickBot="1">
       <c r="A170" s="5">
         <v>111575</v>
       </c>
@@ -3172,7 +3219,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" ht="13.8" thickBot="1">
       <c r="A171" s="5">
         <v>119053</v>
       </c>
@@ -3183,7 +3230,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" ht="13.8" thickBot="1">
       <c r="A172" s="5">
         <v>134321</v>
       </c>
@@ -3194,7 +3241,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" ht="13.8" thickBot="1">
       <c r="A173" s="5">
         <v>124651</v>
       </c>
@@ -3205,7 +3252,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" ht="13.8" thickBot="1">
       <c r="A174" s="5">
         <v>136043</v>
       </c>
@@ -3216,7 +3263,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" ht="13.8" thickBot="1">
       <c r="A175" s="5">
         <v>26896</v>
       </c>
@@ -3227,7 +3274,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" ht="13.8" thickBot="1">
       <c r="A176" s="5">
         <v>103025</v>
       </c>
@@ -3238,7 +3285,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" ht="13.8" thickBot="1">
       <c r="A177" s="5">
         <v>26869</v>
       </c>
@@ -3249,7 +3296,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" ht="13.8" thickBot="1">
       <c r="A178" s="5">
         <v>156291</v>
       </c>
@@ -3260,7 +3307,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" ht="13.8" thickBot="1">
       <c r="A179" s="5">
         <v>112914</v>
       </c>
@@ -3271,7 +3318,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" ht="13.8" thickBot="1">
       <c r="A180" s="5">
         <v>9354</v>
       </c>
@@ -3282,7 +3329,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" ht="13.8" thickBot="1">
       <c r="A181" s="3">
         <v>119588</v>
       </c>
@@ -3293,7 +3340,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" ht="13.8" thickBot="1">
       <c r="A182" s="3">
         <v>119155</v>
       </c>
@@ -3304,7 +3351,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" ht="13.8" thickBot="1">
       <c r="A183" s="3">
         <v>107072</v>
       </c>
@@ -3315,7 +3362,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" ht="13.8" thickBot="1">
       <c r="A184" s="3">
         <v>153402</v>
       </c>
@@ -3326,7 +3373,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" ht="13.8" thickBot="1">
       <c r="A185" s="3">
         <v>110153</v>
       </c>
@@ -3337,7 +3384,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" ht="13.8" thickBot="1">
       <c r="A186" s="3">
         <v>3467</v>
       </c>
@@ -3348,7 +3395,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" ht="13.8" thickBot="1">
       <c r="A187" s="3">
         <v>100653</v>
       </c>
@@ -3359,7 +3406,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" ht="13.8" thickBot="1">
       <c r="A188" s="3">
         <v>3470</v>
       </c>
@@ -3370,7 +3417,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" ht="13.8" thickBot="1">
       <c r="A189" s="3">
         <v>815</v>
       </c>
@@ -3381,7 +3428,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" ht="13.8" thickBot="1">
       <c r="A190" s="3">
         <v>127599</v>
       </c>
@@ -3392,7 +3439,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" ht="13.8" thickBot="1">
       <c r="A191" s="3">
         <v>107073</v>
       </c>
@@ -3403,7 +3450,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" ht="13.8" thickBot="1">
       <c r="A192" s="3">
         <v>102941</v>
       </c>
@@ -3414,7 +3461,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" ht="13.8" thickBot="1">
       <c r="A193" s="3">
         <v>8626</v>
       </c>
@@ -3425,7 +3472,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" ht="13.8" thickBot="1">
       <c r="A194" s="3">
         <v>1483</v>
       </c>
@@ -3436,7 +3483,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" ht="13.8" thickBot="1">
       <c r="A195" s="5">
         <v>1471</v>
       </c>
@@ -3447,7 +3494,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" ht="13.8" thickBot="1">
       <c r="A196" s="5">
         <v>107579</v>
       </c>
@@ -3458,7 +3505,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" ht="13.8" thickBot="1">
       <c r="A197" s="5">
         <v>2505</v>
       </c>
@@ -3469,7 +3516,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" ht="13.8" thickBot="1">
       <c r="A198" s="5">
         <v>1467</v>
       </c>
@@ -3480,7 +3527,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" ht="13.8" thickBot="1">
       <c r="A199" s="5">
         <v>154917</v>
       </c>
@@ -3491,7 +3538,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" ht="13.8" thickBot="1">
       <c r="A200" s="5">
         <v>142558</v>
       </c>
@@ -3502,7 +3549,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" ht="13.8" thickBot="1">
       <c r="A201" s="5">
         <v>3081</v>
       </c>
@@ -3513,7 +3560,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" ht="13.8" thickBot="1">
       <c r="A202" s="5">
         <v>126060</v>
       </c>
@@ -3524,7 +3571,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" ht="13.8" thickBot="1">
       <c r="A203" s="5">
         <v>102312</v>
       </c>
@@ -3535,7 +3582,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" ht="13.8" thickBot="1">
       <c r="A204" s="5">
         <v>144023</v>
       </c>
@@ -3546,7 +3593,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" ht="13.8" thickBot="1">
       <c r="A205" s="7">
         <v>101273</v>
       </c>
@@ -3557,7 +3604,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" ht="13.8" thickBot="1">
       <c r="A206" s="8">
         <v>111038</v>
       </c>
@@ -3568,7 +3615,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" ht="13.8" thickBot="1">
       <c r="A207" s="7">
         <v>102119</v>
       </c>
@@ -3579,7 +3626,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" ht="13.8" thickBot="1">
       <c r="A208" s="8">
         <v>109412</v>
       </c>
@@ -3590,7 +3637,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3" ht="13.8" thickBot="1">
       <c r="A209" s="7">
         <v>103518</v>
       </c>
@@ -3601,7 +3648,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" ht="13.8" thickBot="1">
       <c r="A210" s="8">
         <v>105153</v>
       </c>
@@ -3612,7 +3659,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" ht="13.8" thickBot="1">
       <c r="A211" s="7">
         <v>109929</v>
       </c>
@@ -3623,7 +3670,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" ht="13.8" thickBot="1">
       <c r="A212" s="8">
         <v>1804</v>
       </c>
@@ -3634,7 +3681,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" ht="13.8" thickBot="1">
       <c r="A213" s="7">
         <v>2490</v>
       </c>
@@ -3645,7 +3692,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" ht="13.8" thickBot="1">
       <c r="A214" s="8">
         <v>22911</v>
       </c>
@@ -3656,7 +3703,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" ht="13.8" thickBot="1">
       <c r="A215" s="7">
         <v>135404</v>
       </c>
@@ -3667,7 +3714,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" ht="13.8" thickBot="1">
       <c r="A216" s="8">
         <v>13698</v>
       </c>
@@ -3678,7 +3725,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" ht="13.8" thickBot="1">
       <c r="A217" s="3">
         <v>3356</v>
       </c>
@@ -3689,7 +3736,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" ht="13.8" thickBot="1">
       <c r="A218" s="4">
         <v>3209</v>
       </c>
@@ -3700,7 +3747,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" ht="13.8" thickBot="1">
       <c r="A219" s="3">
         <v>3354</v>
       </c>
@@ -3711,7 +3758,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" ht="13.8" thickBot="1">
       <c r="A220" s="3">
         <v>25853</v>
       </c>
@@ -3722,7 +3769,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" ht="13.8" thickBot="1">
       <c r="A221" s="3">
         <v>17538</v>
       </c>
@@ -3733,7 +3780,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" ht="13.8" thickBot="1">
       <c r="A222" s="3">
         <v>104934</v>
       </c>
@@ -3744,7 +3791,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" ht="13.8" thickBot="1">
       <c r="A223" s="3">
         <v>3204</v>
       </c>
@@ -3755,7 +3802,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" ht="13.8" thickBot="1">
       <c r="A224" s="3">
         <v>8073</v>
       </c>
@@ -3766,7 +3813,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" ht="13.8" thickBot="1">
       <c r="A225" s="3">
         <v>103269</v>
       </c>
@@ -3777,7 +3824,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" ht="13.8" thickBot="1">
       <c r="A226" s="3">
         <v>119166</v>
       </c>
@@ -3788,7 +3835,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" ht="13.8" thickBot="1">
       <c r="A227" s="5">
         <v>103269</v>
       </c>
@@ -3799,7 +3846,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" ht="13.8" thickBot="1">
       <c r="A228" s="5">
         <v>26639</v>
       </c>
@@ -3810,7 +3857,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" ht="13.8" thickBot="1">
       <c r="A229" s="5">
         <v>3615</v>
       </c>
@@ -3821,7 +3868,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" ht="13.8" thickBot="1">
       <c r="A230" s="5">
         <v>8247</v>
       </c>
@@ -3832,7 +3879,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" ht="13.8" thickBot="1">
       <c r="A231" s="5">
         <v>1420</v>
       </c>
@@ -3843,7 +3890,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" ht="13.8" thickBot="1">
       <c r="A232" s="5">
         <v>103865</v>
       </c>
@@ -3854,7 +3901,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" ht="13.8" thickBot="1">
       <c r="A233" s="5">
         <v>14462</v>
       </c>
@@ -3865,7 +3912,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" ht="13.8" thickBot="1">
       <c r="A234" s="5">
         <v>110681</v>
       </c>
@@ -3876,7 +3923,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" ht="13.8" thickBot="1">
       <c r="A235" s="5">
         <v>102622</v>
       </c>
@@ -3887,7 +3934,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" ht="13.8" thickBot="1">
       <c r="A236" s="5">
         <v>127082</v>
       </c>
@@ -3898,7 +3945,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" ht="13.8" thickBot="1">
       <c r="A237" s="7">
         <v>27540</v>
       </c>
@@ -3909,7 +3956,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" ht="13.8" thickBot="1">
       <c r="A238" s="8">
         <v>120265</v>
       </c>
@@ -3920,7 +3967,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" ht="13.8" thickBot="1">
       <c r="A239" s="7">
         <v>108756</v>
       </c>
@@ -3931,7 +3978,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" ht="13.8" thickBot="1">
       <c r="A240" s="7">
         <v>102634</v>
       </c>
@@ -3942,7 +3989,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" ht="13.8" thickBot="1">
       <c r="A241" s="7">
         <v>101283</v>
       </c>
@@ -3953,7 +4000,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" ht="13.8" thickBot="1">
       <c r="A242" s="7">
         <v>2895</v>
       </c>
@@ -3964,7 +4011,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" ht="13.8" thickBot="1">
       <c r="A243" s="8">
         <v>3864</v>
       </c>
@@ -3975,7 +4022,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" ht="13.8" thickBot="1">
       <c r="A244" s="7">
         <v>121277</v>
       </c>
@@ -3986,7 +4033,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" ht="13.8" thickBot="1">
       <c r="A245" s="8">
         <v>3580</v>
       </c>
@@ -3997,7 +4044,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" ht="13.8" thickBot="1">
       <c r="A246" s="8">
         <v>8386</v>
       </c>
@@ -4008,7 +4055,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" ht="13.8" thickBot="1">
       <c r="A247" s="7">
         <v>26398</v>
       </c>
@@ -4019,7 +4066,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" ht="13.8" thickBot="1">
       <c r="A248" s="8">
         <v>2886</v>
       </c>
@@ -4030,7 +4077,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" ht="13.8" thickBot="1">
       <c r="A249" s="7">
         <v>7963</v>
       </c>
@@ -4041,7 +4088,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" ht="13.8" thickBot="1">
       <c r="A250" s="7">
         <v>101480</v>
       </c>
@@ -4052,7 +4099,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" ht="13.8" thickBot="1">
       <c r="A251" s="8">
         <v>104999</v>
       </c>
@@ -4063,7 +4110,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" ht="13.8" thickBot="1">
       <c r="A252" s="8">
         <v>8333</v>
       </c>
@@ -4074,7 +4121,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" ht="13.8" thickBot="1">
       <c r="A253" s="8">
         <v>127424</v>
       </c>
@@ -4085,7 +4132,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" ht="13.8" thickBot="1">
       <c r="A254" s="7">
         <v>133083</v>
       </c>
@@ -4096,7 +4143,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" ht="13.8" thickBot="1">
       <c r="A255" s="8">
         <v>107929</v>
       </c>
@@ -4107,7 +4154,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" ht="13.8" thickBot="1">
       <c r="A256" s="8">
         <v>25902</v>
       </c>
@@ -4118,7 +4165,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" ht="13.8" thickBot="1">
       <c r="A257" s="8">
         <v>27821</v>
       </c>
@@ -4129,7 +4176,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" ht="13.8" thickBot="1">
       <c r="A258" s="8">
         <v>111972</v>
       </c>
@@ -4140,7 +4187,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" ht="13.8" thickBot="1">
       <c r="A259" s="8">
         <v>159</v>
       </c>
@@ -4151,7 +4198,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" ht="13.8" thickBot="1">
       <c r="A260" s="8">
         <v>1627</v>
       </c>
@@ -4162,7 +4209,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" ht="13.8" thickBot="1">
       <c r="A261" s="7">
         <v>1635</v>
       </c>
@@ -4173,7 +4220,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" ht="13.8" thickBot="1">
       <c r="A262" s="8">
         <v>104347</v>
       </c>
@@ -4184,7 +4231,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" ht="13.8" thickBot="1">
       <c r="A263" s="7">
         <v>100253</v>
       </c>
@@ -4195,7 +4242,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" ht="13.8" thickBot="1">
       <c r="A264" s="8">
         <v>3359</v>
       </c>
@@ -4203,6 +4250,138 @@
         <v>263</v>
       </c>
       <c r="C264" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" ht="13.8" thickBot="1">
+      <c r="A265" s="7">
+        <v>147880</v>
+      </c>
+      <c r="B265" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C265" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" ht="13.8" thickBot="1">
+      <c r="A266" s="7">
+        <v>112054</v>
+      </c>
+      <c r="B266" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="C266" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" ht="13.8" thickBot="1">
+      <c r="A267" s="7">
+        <v>8483</v>
+      </c>
+      <c r="B267" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="C267" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" ht="13.8" thickBot="1">
+      <c r="A268" s="7">
+        <v>2004</v>
+      </c>
+      <c r="B268" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="C268" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" ht="13.8" thickBot="1">
+      <c r="A269" s="7">
+        <v>19038</v>
+      </c>
+      <c r="B269" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="C269" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" ht="13.8" thickBot="1">
+      <c r="A270" s="7">
+        <v>109366</v>
+      </c>
+      <c r="B270" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C270" s="11">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" ht="13.8" thickBot="1">
+      <c r="A271" s="7">
+        <v>3090</v>
+      </c>
+      <c r="B271" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C271" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" ht="13.8" thickBot="1">
+      <c r="A272" s="7">
+        <v>147085</v>
+      </c>
+      <c r="B272" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="C272" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" ht="13.8" thickBot="1">
+      <c r="A273" s="7">
+        <v>121645</v>
+      </c>
+      <c r="B273" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="C273" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" ht="13.8" thickBot="1">
+      <c r="A274" s="7">
+        <v>174657</v>
+      </c>
+      <c r="B274" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="C274" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" ht="13.8" thickBot="1">
+      <c r="A275" s="7">
+        <v>25775</v>
+      </c>
+      <c r="B275" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="C275" s="11">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" ht="13.8" thickBot="1">
+      <c r="A276" s="7">
+        <v>101284</v>
+      </c>
+      <c r="B276" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C276" s="11">
         <v>59</v>
       </c>
     </row>
